--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4180,8 +4296,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:S14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4202,332 +4322,229 @@
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꼭두각시 — 민요채보-3/꼭두각시.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">꼭두각시</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="15"/>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="E3" s="15"/>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" s="16"/>
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 黃</t>
         </is>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="15"/>
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="O3" s="15"/>
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="Q3" s="15"/>
+      <c r="R3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="S3" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S3" s="15"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K4" s="17"/>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="M4" s="17"/>
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O4" s="17"/>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="S4" s="17"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="E5" s="18"/>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 黃
 潢</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="18"/>
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 無
 潢</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="18"/>
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="18"/>
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="Q5" s="18"/>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S5" s="18"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="15"/>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑
@@ -4535,165 +4552,190 @@
 姑</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="15"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="G6" s="15"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K6" s="15"/>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 姑</t>
         </is>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="M6" s="15"/>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S6" s="2"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="Q6" s="15"/>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S6" s="15"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="C7" s="17"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="17"/>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 南
 仲</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K7" s="17"/>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="17"/>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S7" s="17"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢
 無
 姑</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢
 潢</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="18"/>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="G8" s="18"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K8" s="18"/>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="18"/>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞
@@ -4701,38 +4743,41 @@
 潢</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S8" s="2"/>
-    </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="O8" s="18"/>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S8" s="18"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="15"/>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑
@@ -4740,348 +4785,345 @@
 姑</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="15"/>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="15"/>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 姑</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K9" s="15"/>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="15"/>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S9" s="2"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="O9" s="15"/>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="17"/>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 姑</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="17"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="17"/>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M10" s="17"/>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="S10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="18"/>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="K11" s="18"/>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M11" s="18"/>
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="O11" s="18"/>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="S11" s="18"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="15"/>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="15"/>
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="I12" s="15"/>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="O12" s="15"/>
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="Q12" s="15"/>
+      <c r="R12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="S12" s="15"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="E13" s="17"/>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="I13" s="17"/>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O13" s="17"/>
+      <c r="P13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="S13" s="17"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="18"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="18"/>
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="G14" s="18"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O14" s="18"/>
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="Q14" s="18"/>
+      <c r="R14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S14" s="2"/>
+      <c r="S14" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:S2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="67"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -361,7 +361,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 16정간 격자, 굵은 선 4칸마다 → 4/4·16. 상단 제목 칸 "꼭두각시(자진머리) (2번)". 율명 열 10개 중 맨 오른쪽 열(1줄)과 가운데 열(6줄)은 비어 있어 내용은 2~5줄, 7~10줄. 가사 칸은 모두 비어 있음. 율명 옆 작은 ▼ 표시와 ∴ 점, 율명 몇 개에 친 동그라미(潢), 체크 표시, 상단 ② 와 화살표 곡선은 기호표에 없어 생략. 같은 가락(姑―仲/南^/潢無南/仲姑△ 등) 반복은 같은 글자로 통일. AI 재판독 초안.</t>
+          <t xml:space="preserve">손으로 그린 16정간 격자, 굵은 선 4칸마다 → 4/4·16. 상단 제목 칸 "꼭두각시(자진머리) (2번)". 율명 열 10개 중 맨 오른쪽 열(1줄)과 가운데 열(6줄)은 비어 있어 내용은 2~5줄, 7~10줄. 가사 칸은 모두 비어 있음. 율명 옆 작은 ▼ 표시와 ∴ 점, 율명 몇 개에 친 동그라미(潢), 체크 표시, 상단 ② 와 화살표 곡선은 기호표에 없어 생략. 같은 가락(姑–仲/南^/潢無南/仲姑△ 등) 반복은 같은 글자로 통일. AI 재판독 초안.</t>
         </is>
       </c>
     </row>
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -549,13 +549,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―|仲</t>
+          <t xml:space="preserve">姑|–|仲</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -691,14 +691,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢|―</t>
+          <t xml:space="preserve">無|潢|–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -741,7 +741,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">첫 潢의 氵가 ―처럼 보임</t>
+          <t xml:space="preserve">첫 潢의 氵가 –처럼 보임</t>
         </is>
       </c>
       <c r="K7" s="2"/>
@@ -991,14 +991,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|南|―</t>
+          <t xml:space="preserve">姑|南|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="2"/>
@@ -2083,13 +2083,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南^|―</t>
+          <t xml:space="preserve">南^|–</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="I44" s="2"/>
@@ -2303,13 +2303,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―|仲</t>
+          <t xml:space="preserve">姑|–|仲</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -2445,14 +2445,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢|―</t>
+          <t xml:space="preserve">無|潢|–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2591,14 +2591,14 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢|―</t>
+          <t xml:space="preserve">無|潢|–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -2808,13 +2808,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南^|―</t>
+          <t xml:space="preserve">南^|–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -2881,14 +2881,14 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲|―</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3177,14 +3177,14 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢|―</t>
+          <t xml:space="preserve">無|潢|–</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I74" s="2"/>
@@ -3288,21 +3288,21 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|姑|―|△</t>
+          <t xml:space="preserve">仲|姑|–|△</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
-―
+–
 △</t>
         </is>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑 뒤 작은 ―△</t>
+          <t xml:space="preserve">姑 뒤 작은 –△</t>
         </is>
       </c>
       <c r="K77" s="2"/>
@@ -3330,14 +3330,14 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢|―</t>
+          <t xml:space="preserve">無|潢|–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -3403,13 +3403,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|無</t>
+          <t xml:space="preserve">潢|–|無</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 無</t>
         </is>
       </c>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲|―</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I82" s="2"/>
@@ -3695,13 +3695,13 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南^|―</t>
+          <t xml:space="preserve">南^|–</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="I88" s="2"/>
@@ -3768,14 +3768,14 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲|―</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I90" s="2"/>
@@ -3916,13 +3916,13 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―|仲</t>
+          <t xml:space="preserve">姑|–|仲</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -4099,13 +4099,13 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|姑</t>
+          <t xml:space="preserve">仲|–|姑</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -4173,13 +4173,13 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|姑</t>
+          <t xml:space="preserve">仲|–|姑</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -4247,13 +4247,13 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|姑</t>
+          <t xml:space="preserve">仲|–|姑</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -4321,13 +4321,13 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|姑</t>
+          <t xml:space="preserve">仲|–|姑</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -4428,13 +4428,13 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南^|―</t>
+          <t xml:space="preserve">南^|–</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="I108" s="2"/>
@@ -4501,14 +4501,14 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲|―</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I110" s="3"/>
@@ -4723,12 +4723,12 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I116" s="2"/>
@@ -4758,12 +4758,12 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I117" s="2"/>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I118" s="2"/>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I119" s="2"/>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I120" s="2"/>
@@ -4991,7 +4991,7 @@
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="G3" s="8"/>
@@ -4999,7 +4999,7 @@
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I3" s="8"/>
@@ -5008,7 +5008,7 @@
       <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -5031,7 +5031,7 @@
       <c r="R3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -5050,7 +5050,7 @@
       <c r="D4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -5106,7 +5106,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="9"/>
@@ -5169,14 +5169,14 @@
       <c r="A6" s="0"/>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -5232,7 +5232,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="8"/>
@@ -5262,7 +5262,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="M7" s="8"/>
@@ -5284,7 +5284,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="S7" s="8"/>
@@ -5295,14 +5295,14 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -5354,7 +5354,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C9" s="9"/>
@@ -5369,7 +5369,7 @@
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="G9" s="9"/>
@@ -5429,7 +5429,7 @@
       <c r="D10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -5501,7 +5501,7 @@
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="8"/>
@@ -5509,7 +5509,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="8"/>
@@ -5519,7 +5519,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="M11" s="8"/>
@@ -5613,7 +5613,7 @@
       <c r="D13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="E13" s="9"/>
@@ -5646,7 +5646,7 @@
       <c r="N13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="O13" s="9"/>
@@ -5693,7 +5693,7 @@
         <is>
           <t xml:space="preserve">仲
 姑
-―
+–
 △</t>
         </is>
       </c>
@@ -5743,14 +5743,14 @@
         <is>
           <t xml:space="preserve">仲
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 仲</t>
         </is>
       </c>
@@ -5759,7 +5759,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I15" s="8"/>
@@ -5791,7 +5791,7 @@
         <is>
           <t xml:space="preserve">姑
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="S15" s="8"/>
@@ -5877,7 +5877,7 @@
       <c r="H17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 無</t>
         </is>
       </c>
@@ -5887,7 +5887,7 @@
       <c r="L17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="9"/>

--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4946,750 +4987,750 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">꼭두각시</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 南</t>
         </is>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="24"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 –</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 –</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="I3" s="22"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
 仲</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="M3" s="22"/>
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
 無</t>
         </is>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="O3" s="24"/>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 㳞</t>
         </is>
       </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="Q3" s="22"/>
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
 仲</t>
         </is>
       </c>
-      <c r="S3" s="8"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="8"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 姑</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △
 㴌</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △
 㴌</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="Q4" s="25"/>
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="9"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="25"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="25"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="I5" s="25"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="25"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
 無</t>
         </is>
       </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="25"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="Q5" s="25"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="S5" s="9"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="9"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="26"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 姑</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="26"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 △</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 △</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="I6" s="26"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="26"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="26"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="Q6" s="26"/>
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="10"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 △
 南</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="22"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="22"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="I7" s="22"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 –</t>
         </is>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="22"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
 無</t>
         </is>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="22"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="Q7" s="22"/>
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 –</t>
         </is>
       </c>
-      <c r="S7" s="8"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="8"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 姑</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="25"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="I8" s="25"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="25"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="25"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="18" t="inlineStr">
+      <c r="Q8" s="25"/>
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △
 南</t>
         </is>
       </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="9"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="25"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
 –</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="G9" s="25"/>
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 無</t>
         </is>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="I9" s="27"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="25"/>
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 △
 㳞</t>
         </is>
       </c>
-      <c r="O9" s="9"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="O9" s="25"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 △
 㳞</t>
         </is>
       </c>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="Q9" s="25"/>
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南
 潢</t>
         </is>
       </c>
-      <c r="S9" s="9"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="9"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 姑</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 △</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="26"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="26"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="Q10" s="26"/>
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 △
 南</t>
         </is>
       </c>
-      <c r="S10" s="10"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="10"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="22"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 –</t>
         </is>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 –</t>
         </is>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="I11" s="22"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 –</t>
         </is>
       </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="22"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="22"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
 無</t>
         </is>
       </c>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="Q11" s="22"/>
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 △
 㴌</t>
         </is>
       </c>
-      <c r="S11" s="8"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="8"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="21"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △
 㴌</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △
 㴌</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="I12" s="25"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="25"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="25"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="Q12" s="25"/>
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △
 南</t>
         </is>
       </c>
-      <c r="S12" s="9"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="9"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
 –</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
 –</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 △
 㳞</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南
 潢</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="9"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 △‹</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
@@ -5697,287 +5738,287 @@
 △</t>
         </is>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="I14" s="28"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 △</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="26"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="26"/>
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 △
 南</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="10"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="26"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 –</t>
         </is>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="24"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
 仲</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="22"/>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 –</t>
         </is>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="I15" s="22"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="M15" s="22"/>
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 姑</t>
         </is>
       </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="O15" s="22"/>
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
 無·</t>
         </is>
       </c>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="Q15" s="22"/>
+      <c r="R15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南
 –</t>
         </is>
       </c>
-      <c r="S15" s="8"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="8"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △
 㴌</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="25"/>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="I16" s="25"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="M16" s="25"/>
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="O16" s="25"/>
+      <c r="P16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="17" t="inlineStr">
+      <c r="Q16" s="25"/>
+      <c r="R16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="S16" s="9"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="9"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="25"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="25"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 無</t>
         </is>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="I17" s="25"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
 –</t>
         </is>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="M17" s="25"/>
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="O17" s="9"/>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="O17" s="25"/>
+      <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 △
 㳞</t>
         </is>
       </c>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="17" t="inlineStr">
+      <c r="Q17" s="25"/>
+      <c r="R17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="S17" s="9"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="9"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 △</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="26"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="26"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="I18" s="26"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 南</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="M18" s="26"/>
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="O18" s="26"/>
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="17" t="inlineStr">
+      <c r="Q18" s="26"/>
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="S18" s="10"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="10"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -4960,32 +4960,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="108.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
       <c r="T3" s="21"/>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="108.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="108.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="108.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -5589,7 +5589,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -5647,7 +5647,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -5710,7 +5710,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -5776,7 +5776,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="108.96" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5824,7 +5824,7 @@
         <is>
           <t xml:space="preserve">無
 汰
-無·</t>
+無–</t>
         </is>
       </c>
       <c r="Q15" s="22"/>
@@ -5839,7 +5839,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="108.96" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -5897,7 +5897,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="108.96" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -5959,7 +5959,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="108.96" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>

--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -3920,14 +3920,14 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|姑|△‹</t>
+          <t xml:space="preserve">仲|姑|△</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="I93" s="2"/>
@@ -5726,7 +5726,7 @@
         <is>
           <t xml:space="preserve">仲
 姑
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="G14" s="26"/>

--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -435,7 +435,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -445,7 +444,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -454,7 +452,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -470,7 +467,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -479,17 +476,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -522,6 +519,12 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -614,7 +617,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -672,6 +675,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4632,644 +4679,644 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="21"/>
+      <c r="F3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="7" t="s">
+      <c r="I3" s="19"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="9" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="7" t="s">
+      <c r="O3" s="21"/>
+      <c r="P3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="7" t="s">
+      <c r="Q3" s="19"/>
+      <c r="R3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="8"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="8"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="7" t="s">
+      <c r="I4" s="22"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="7" t="s">
+      <c r="M4" s="22"/>
+      <c r="N4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="7" t="s">
+      <c r="O4" s="22"/>
+      <c r="P4" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="7" t="s">
+      <c r="Q4" s="22"/>
+      <c r="R4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="11"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="22"/>
     </row>
     <row r="5" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="22"/>
+      <c r="D5" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="7" t="s">
+      <c r="I5" s="22"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="7" t="s">
+      <c r="M5" s="22"/>
+      <c r="N5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="7" t="s">
+      <c r="O5" s="22"/>
+      <c r="P5" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="7" t="s">
+      <c r="Q5" s="22"/>
+      <c r="R5" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="11"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="7" t="s">
+      <c r="I6" s="23"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="7" t="s">
+      <c r="M6" s="23"/>
+      <c r="N6" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="12"/>
-      <c r="P6" s="7" t="s">
+      <c r="O6" s="23"/>
+      <c r="P6" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="7" t="s">
+      <c r="Q6" s="23"/>
+      <c r="R6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="12"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="19"/>
+      <c r="H7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7" t="s">
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="7" t="s">
+      <c r="M7" s="19"/>
+      <c r="N7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="7" t="s">
+      <c r="O7" s="19"/>
+      <c r="P7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="7" t="s">
+      <c r="Q7" s="19"/>
+      <c r="R7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="S7" s="8"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="8"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="22"/>
+      <c r="D8" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="22"/>
+      <c r="F8" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="22"/>
+      <c r="H8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="7" t="s">
+      <c r="I8" s="22"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="7" t="s">
+      <c r="M8" s="22"/>
+      <c r="N8" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="7" t="s">
+      <c r="O8" s="22"/>
+      <c r="P8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="9" t="s">
+      <c r="Q8" s="22"/>
+      <c r="R8" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="13"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="11"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="22"/>
+      <c r="D9" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="9" t="s">
+      <c r="G9" s="22"/>
+      <c r="H9" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="7" t="s">
+      <c r="I9" s="24"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="7" t="s">
+      <c r="M9" s="22"/>
+      <c r="N9" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="7" t="s">
+      <c r="O9" s="22"/>
+      <c r="P9" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="7" t="s">
+      <c r="Q9" s="22"/>
+      <c r="R9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="S9" s="11"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="11"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="23"/>
+      <c r="F10" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="7" t="s">
+      <c r="I10" s="23"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="7" t="s">
+      <c r="M10" s="23"/>
+      <c r="N10" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="7" t="s">
+      <c r="O10" s="23"/>
+      <c r="P10" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="7" t="s">
+      <c r="Q10" s="23"/>
+      <c r="R10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="12"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="7" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="19"/>
+      <c r="F11" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="19"/>
+      <c r="H11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7" t="s">
+      <c r="I11" s="19"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="7" t="s">
+      <c r="M11" s="19"/>
+      <c r="N11" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="7" t="s">
+      <c r="O11" s="19"/>
+      <c r="P11" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="7" t="s">
+      <c r="Q11" s="19"/>
+      <c r="R11" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="S11" s="8"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="8"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="19"/>
     </row>
     <row r="12" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="7" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="7" t="s">
+      <c r="E12" s="22"/>
+      <c r="F12" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="7" t="s">
+      <c r="G12" s="22"/>
+      <c r="H12" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="7" t="s">
+      <c r="I12" s="22"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="7" t="s">
+      <c r="M12" s="22"/>
+      <c r="N12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="7" t="s">
+      <c r="O12" s="22"/>
+      <c r="P12" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="7" t="s">
+      <c r="Q12" s="22"/>
+      <c r="R12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="11"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
+      <c r="B13" s="18"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7" t="s">
+      <c r="I13" s="22"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="7" t="s">
+      <c r="M13" s="22"/>
+      <c r="N13" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="7" t="s">
+      <c r="O13" s="22"/>
+      <c r="P13" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="7" t="s">
+      <c r="Q13" s="22"/>
+      <c r="R13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="11"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="7" t="s">
+      <c r="B14" s="18"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="9" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="7" t="s">
+      <c r="I14" s="25"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="7" t="s">
+      <c r="M14" s="23"/>
+      <c r="N14" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="O14" s="12"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="23"/>
+      <c r="P14" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="7" t="s">
+      <c r="Q14" s="23"/>
+      <c r="R14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="S14" s="12"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="12"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="7" t="s">
+      <c r="E15" s="21"/>
+      <c r="F15" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7" t="s">
+      <c r="G15" s="19"/>
+      <c r="H15" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7" t="s">
+      <c r="I15" s="19"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="7" t="s">
+      <c r="M15" s="19"/>
+      <c r="N15" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="7" t="s">
+      <c r="O15" s="19"/>
+      <c r="P15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="7" t="s">
+      <c r="Q15" s="19"/>
+      <c r="R15" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="S15" s="8"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="8"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="7" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="7" t="s">
+      <c r="E16" s="22"/>
+      <c r="F16" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="7" t="s">
+      <c r="G16" s="22"/>
+      <c r="H16" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="7" t="s">
+      <c r="I16" s="22"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="7" t="s">
+      <c r="M16" s="22"/>
+      <c r="N16" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="7" t="s">
+      <c r="O16" s="22"/>
+      <c r="P16" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="7" t="s">
+      <c r="Q16" s="22"/>
+      <c r="R16" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="11"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="7" t="s">
+      <c r="B17" s="18"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="7" t="s">
+      <c r="E17" s="22"/>
+      <c r="F17" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="7" t="s">
+      <c r="G17" s="22"/>
+      <c r="H17" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="7" t="s">
+      <c r="I17" s="22"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="7" t="s">
+      <c r="M17" s="22"/>
+      <c r="N17" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="7" t="s">
+      <c r="O17" s="22"/>
+      <c r="P17" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="7" t="s">
+      <c r="Q17" s="22"/>
+      <c r="R17" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="S17" s="11"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="11"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="108.96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="7" t="s">
+      <c r="B18" s="18"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="7" t="s">
+      <c r="E18" s="23"/>
+      <c r="F18" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="23"/>
+      <c r="H18" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="7" t="s">
+      <c r="I18" s="23"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="7" t="s">
+      <c r="M18" s="23"/>
+      <c r="N18" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="O18" s="12"/>
-      <c r="P18" s="7" t="s">
+      <c r="O18" s="23"/>
+      <c r="P18" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="7" t="s">
+      <c r="Q18" s="23"/>
+      <c r="R18" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="S18" s="12"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="12"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -541,10 +541,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/꼭두각시.xlsx
+++ b/sheets/민요/검수/꼭두각시.xlsx
@@ -4584,25 +4584,25 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="8" width="6"/>
   </cols>
   <sheetData>
